--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27113-2025 artfynd.xlsx
+++ b/artfynd/A 27113-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017476</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>92529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017475</v>
       </c>
       <c r="B3" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
